--- a/cuadros/ABRIL_GUACARA_IPSFA.xlsx
+++ b/cuadros/ABRIL_GUACARA_IPSFA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AA0FF5-E2F2-4171-AA78-C8C60086F9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45AB59F-C2C2-44F5-99C3-F6C5A3D1895F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="72">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -134,9 +134,6 @@
     <t>IPSFA</t>
   </si>
   <si>
-    <t>IPFSA</t>
-  </si>
-  <si>
     <t>LATIN FRUTS</t>
   </si>
   <si>
@@ -249,6 +246,9 @@
   </si>
   <si>
     <t>00114739</t>
+  </si>
+  <si>
+    <t>00170489</t>
   </si>
 </sst>
 </file>
@@ -696,7 +696,7 @@
         <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2">
         <v>12705</v>
@@ -705,10 +705,10 @@
         <v>46113</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
         <v>24</v>
@@ -718,7 +718,7 @@
         <v>TIPO C</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J2" s="5">
         <v>140</v>
@@ -729,7 +729,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>12659</v>
@@ -738,10 +738,10 @@
         <v>46113</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
         <v>22</v>
@@ -751,7 +751,7 @@
         <v>TIPO C</v>
       </c>
       <c r="I3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J3" s="5">
         <v>4</v>
@@ -762,7 +762,7 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4">
         <v>13338</v>
@@ -771,10 +771,10 @@
         <v>46113</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
         <v>24</v>
@@ -784,7 +784,7 @@
         <v>TIPO C</v>
       </c>
       <c r="I4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.4">
@@ -792,7 +792,7 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5">
         <v>19069</v>
@@ -801,10 +801,10 @@
         <v>46119</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
@@ -814,7 +814,7 @@
         <v>TIPO B</v>
       </c>
       <c r="I5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.4">
@@ -822,7 +822,7 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6">
         <v>408</v>
@@ -831,10 +831,10 @@
         <v>46115</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -844,7 +844,7 @@
         <v>TIPO E</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J6" s="5">
         <v>473.92</v>
@@ -855,7 +855,7 @@
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7">
         <v>13369</v>
@@ -864,10 +864,10 @@
         <v>46120</v>
       </c>
       <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
         <v>44</v>
-      </c>
-      <c r="F7" t="s">
-        <v>45</v>
       </c>
       <c r="G7" t="s">
         <v>22</v>
@@ -877,7 +877,7 @@
         <v>TIPO C</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J7" s="5">
         <v>2.4</v>
@@ -888,7 +888,7 @@
         <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H8" t="str">
         <f>IF(G8="","",VLOOKUP(G8,REFERENCIA!$A$1:$B$15,2,0))</f>
@@ -900,7 +900,7 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9">
         <v>430</v>
@@ -909,10 +909,10 @@
         <v>46121</v>
       </c>
       <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
         <v>44</v>
-      </c>
-      <c r="F9" t="s">
-        <v>45</v>
       </c>
       <c r="G9" t="s">
         <v>27</v>
@@ -922,10 +922,13 @@
         <v>TIPO D</v>
       </c>
       <c r="I9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J9" s="4">
         <v>0.74</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.4">
@@ -933,7 +936,7 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>9356</v>
@@ -942,10 +945,10 @@
         <v>46122</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
@@ -955,7 +958,7 @@
         <v>TIPO C</v>
       </c>
       <c r="I10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J10" s="5">
         <v>82.12</v>
@@ -966,7 +969,7 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>23430</v>
@@ -975,10 +978,10 @@
         <v>46122</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -988,7 +991,7 @@
         <v>TIPO B</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.4">
@@ -996,7 +999,7 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>6134</v>
@@ -1005,10 +1008,10 @@
         <v>46122</v>
       </c>
       <c r="E12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
         <v>30</v>
@@ -1018,7 +1021,7 @@
         <v>TIPO E</v>
       </c>
       <c r="I12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.4">
@@ -1026,7 +1029,7 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>8683</v>
@@ -1035,10 +1038,10 @@
         <v>46128</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
@@ -1048,7 +1051,7 @@
         <v>TIPO B</v>
       </c>
       <c r="I13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">
@@ -1056,16 +1059,16 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="3">
         <v>46128</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
@@ -1075,7 +1078,7 @@
         <v>TIPO B</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.4">
@@ -1083,7 +1086,7 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>23847</v>
@@ -1092,10 +1095,10 @@
         <v>46129</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s">
         <v>19</v>
@@ -1105,7 +1108,7 @@
         <v>TIPO B</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
@@ -1113,7 +1116,7 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16">
         <v>13439</v>
@@ -1122,10 +1125,10 @@
         <v>46129</v>
       </c>
       <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" t="s">
         <v>44</v>
-      </c>
-      <c r="F16" t="s">
-        <v>45</v>
       </c>
       <c r="G16" t="s">
         <v>27</v>
@@ -1135,13 +1138,13 @@
         <v>TIPO D</v>
       </c>
       <c r="I16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J16" s="4">
         <v>0.4</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.4">
@@ -1149,7 +1152,7 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17">
         <v>12912</v>
@@ -1158,10 +1161,10 @@
         <v>46129</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G17" t="s">
         <v>27</v>
@@ -1171,13 +1174,13 @@
         <v>TIPO D</v>
       </c>
       <c r="I17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J17" s="4">
         <v>0.3</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
@@ -1185,7 +1188,7 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>3947</v>
@@ -1194,10 +1197,10 @@
         <v>46133</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
         <v>17</v>
@@ -1207,15 +1210,15 @@
         <v>TIPO B</v>
       </c>
       <c r="I18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
         <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
       </c>
       <c r="C19">
         <v>6384</v>
@@ -1224,10 +1227,10 @@
         <v>46139</v>
       </c>
       <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="s">
         <v>44</v>
-      </c>
-      <c r="F19" t="s">
-        <v>45</v>
       </c>
       <c r="G19" t="s">
         <v>23</v>
@@ -1237,7 +1240,7 @@
         <v>TIPO C</v>
       </c>
       <c r="I19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
@@ -1245,7 +1248,7 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20">
         <v>6427</v>
@@ -1254,10 +1257,10 @@
         <v>46140</v>
       </c>
       <c r="E20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1267,7 +1270,7 @@
         <v>TIPO B</v>
       </c>
       <c r="I20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.4">
